--- a/docs/electrical-grid/categories/lighting/register.xlsx
+++ b/docs/electrical-grid/categories/lighting/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R914606010f14439e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rcb474525ac7a41c7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R30e5fa98bf134ff1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R36375076126041c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R80d8b68cea734325"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Re9faecadda1e4aed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R769b810bbb234d73"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R2278c82fcd614d95"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -487,7 +487,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Lighting. Reading, sanctuary, circulation, paths, facade and festival exterior lighting. Model snapshot: 2026-10-07T00:43:44.962Z.</x:v>
+        <x:v>Lighting. Reading, sanctuary, circulation, paths, facade and festival exterior lighting. Model snapshot: 2026-10-07T08:19:57.914Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -570,7 +570,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>ec066f78b134a4ab41e86b94133226ce6f6438520682c580b116eb56ed715fc9</x:v>
+        <x:v>682cddfb34b9ba0867e0152518ab5a1ad129de7bbb8828a58f64d23cf072cc71</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -578,7 +578,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>99ba5edfb5f5ec7966456e3ad66285380fe1c91036b9f85ff7846b14c7fd32f2</x:v>
+        <x:v>4139f272a1dd534c1fd927881b22bba0c4b16ce3b4162f405c44d3aab380f491</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -1153,7 +1153,7 @@
         <x:v>drop:LC1:L1:light:-1:L3</x:v>
       </x:c>
       <x:c r="AC9" s="8" t="str">
-        <x:v>{"lumens":2300,"dim":1,"anchorY":10.394880434782609}</x:v>
+        <x:v>{"lumens":2300,"dim":1,"anchorY":8.59}</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="96" customHeight="1">
@@ -16149,7 +16149,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31ec3285a43f4964"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d9184e961bf406e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16633,7 +16633,7 @@
       </x:c>
       <x:c r="I10" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$1350,A10,'Route Points'!$F$7:$F$1350)</x:f>
-        <x:v>8.3917306647131</x:v>
+        <x:v>7.005000000000001</x:v>
       </x:c>
       <x:c r="J10" s="11"/>
       <x:c r="K10" s="11" t="str">
@@ -31283,7 +31283,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5de6db1e7c604cf2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb57a2ac7bda462d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -32084,14 +32084,14 @@
         <x:v>9.975</x:v>
       </x:c>
       <x:c r="D36" s="11" t="n">
-        <x:v>7.02</x:v>
+        <x:v>6.83</x:v>
       </x:c>
       <x:c r="E36" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F36" s="11" t="n">
         <x:f>SQRT((C36-C35)^2+(D36-D35)^2+(E36-E35)^2)</x:f>
-        <x:v>0.6699999999999999</x:v>
+        <x:v>0.4800000000000004</x:v>
       </x:c>
       <x:c r="G36" s="8" t="str">
         <x:v>Current</x:v>
@@ -32108,14 +32108,14 @@
         <x:v>9.975</x:v>
       </x:c>
       <x:c r="D37" s="11" t="n">
-        <x:v>7.065002717391305</x:v>
+        <x:v>6.83</x:v>
       </x:c>
       <x:c r="E37" s="11" t="n">
-        <x:v>-7.05</x:v>
+        <x:v>-3.6</x:v>
       </x:c>
       <x:c r="F37" s="11" t="n">
         <x:f>SQRT((C37-C36)^2+(D37-D36)^2+(E37-E36)^2)</x:f>
-        <x:v>0.3132494925336704</x:v>
+        <x:v>3.7600000000000002</x:v>
       </x:c>
       <x:c r="G37" s="8" t="str">
         <x:v>Current</x:v>
@@ -32132,14 +32132,14 @@
         <x:v>9.975</x:v>
       </x:c>
       <x:c r="D38" s="11" t="n">
-        <x:v>10.294880434782609</x:v>
+        <x:v>8.59</x:v>
       </x:c>
       <x:c r="E38" s="11" t="n">
-        <x:v>-2.6</x:v>
+        <x:v>-3.6</x:v>
       </x:c>
       <x:c r="F38" s="11" t="n">
         <x:f>SQRT((C38-C37)^2+(D38-D37)^2+(E38-E37)^2)</x:f>
-        <x:v>5.49860073739682</x:v>
+        <x:v>1.7599999999999998</x:v>
       </x:c>
       <x:c r="G38" s="8" t="str">
         <x:v>Current</x:v>
@@ -32156,14 +32156,14 @@
         <x:v>9.975</x:v>
       </x:c>
       <x:c r="D39" s="11" t="n">
-        <x:v>10.394880434782609</x:v>
+        <x:v>8.59</x:v>
       </x:c>
       <x:c r="E39" s="11" t="n">
         <x:v>-2.6</x:v>
       </x:c>
       <x:c r="F39" s="11" t="n">
         <x:f>SQRT((C39-C38)^2+(D39-D38)^2+(E39-E38)^2)</x:f>
-        <x:v>0.09999999999999964</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G39" s="8" t="str">
         <x:v>Current</x:v>
@@ -32187,7 +32187,7 @@
       </x:c>
       <x:c r="F40" s="11" t="n">
         <x:f>SQRT((C40-C39)^2+(D40-D39)^2+(E40-E39)^2)</x:f>
-        <x:v>1.8098804347826096</x:v>
+        <x:v>0.005000000000000782</x:v>
       </x:c>
       <x:c r="G40" s="8" t="str">
         <x:v>Current</x:v>
@@ -63639,7 +63639,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R693f139004824509"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re5195799a7d2489e"/>
   </x:tableParts>
 </x:worksheet>
 </file>